--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486891_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486891_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.463</v>
+        <v>3.0931</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1708</v>
+        <v>1.5045</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2922</v>
+        <v>1.5886</v>
       </c>
       <c r="G2" t="n">
         <v>0.8280999999999999</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.248</v>
+        <v>-0.618</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5533</v>
+        <v>0.8869</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.8013</v>
+        <v>-1.5049</v>
       </c>
       <c r="V2" t="n">
         <v>0.8295</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6814</v>
+        <v>1.9755</v>
       </c>
       <c r="E3" t="n">
-        <v>2.273</v>
+        <v>3.6461</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4083</v>
+        <v>-1.6706</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0387</v>
+        <v>4.4158</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4752</v>
+        <v>-0.117</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4364</v>
+        <v>4.5328</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1691</v>
+        <v>5.6567</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0507</v>
+        <v>0.6847</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>4.972</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1304</v>
+        <v>-1.2408</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4244</v>
+        <v>-0.8017</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5548</v>
+        <v>-0.4391</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.616</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2588</v>
+        <v>-3.0801</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6078</v>
+        <v>0.0319</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7117</v>
+        <v>0.4802</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.104</v>
+        <v>-0.4483</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3491</v>
+        <v>-0.8295</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3491</v>
+        <v>0.5893</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7564</v>
+        <v>1.5627</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5916</v>
+        <v>0.4816</v>
       </c>
       <c r="F4" t="n">
-        <v>1.348</v>
+        <v>1.0812</v>
       </c>
       <c r="G4" t="n">
         <v>0.6435</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3245</v>
+        <v>-0.5181</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6046</v>
+        <v>0.4685</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7199</v>
+        <v>-0.9867</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4469</v>
+        <v>1.2441</v>
       </c>
       <c r="E5" t="n">
-        <v>2.325</v>
+        <v>0.8357</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8781</v>
+        <v>0.4083</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4158</v>
+        <v>2.0387</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.117</v>
+        <v>2.4752</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5328</v>
+        <v>-0.4364</v>
       </c>
       <c r="J5" t="n">
-        <v>5.6567</v>
+        <v>2.1691</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6847</v>
+        <v>2.0507</v>
       </c>
       <c r="L5" t="n">
-        <v>4.972</v>
+        <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2408</v>
+        <v>-0.1304</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8017</v>
+        <v>0.4244</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4391</v>
+        <v>-0.5548</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6427</v>
+        <v>-0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0801</v>
+        <v>-2.2588</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4967</v>
+        <v>0.1705</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8409</v>
+        <v>1.2745</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6558</v>
+        <v>-1.104</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8295</v>
+        <v>-0.3491</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>-0.3491</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0785</v>
+        <v>-0.5325</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.5986</v>
+        <v>-3.6761</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6772</v>
+        <v>3.1436</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7101</v>
@@ -922,13 +922,13 @@
         <v>2.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3143</v>
+        <v>0.7032</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0613</v>
+        <v>0.9838</v>
       </c>
       <c r="U6" t="n">
-        <v>0.253</v>
+        <v>-0.2806</v>
       </c>
       <c r="V6" t="n">
         <v>1.5277</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.5324</v>
+        <v>-3.4052</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1593</v>
+        <v>-5.4225</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3731</v>
+        <v>2.0173</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.0674</v>
+        <v>-1.7587</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9335</v>
+        <v>-1.956</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1338</v>
+        <v>0.1973</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8763</v>
+        <v>-2.5785</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2974</v>
+        <v>-2.3543</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.579</v>
+        <v>-0.2241</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.191</v>
+        <v>0.8198</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6362</v>
+        <v>0.3983</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5549</v>
+        <v>0.4215</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2321</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>-3.4908</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>2.6694</v>
       </c>
       <c r="S7" t="n">
-        <v>1.767</v>
+        <v>-1.0654</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7704</v>
+        <v>0.4065</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0034</v>
+        <v>-1.472</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.4071</v>
+        <v>-4.4961</v>
       </c>
       <c r="E8" t="n">
         <v>-0.5810999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.826</v>
+        <v>-3.915</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0487</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6172</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3952</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2219</v>
+        <v>-0.3109</v>
       </c>
       <c r="V8" t="n">
         <v>-3.5359</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3959</v>
+        <v>-4.6921</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.0574</v>
+        <v>-3.3487</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6616</v>
+        <v>-1.3434</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7587</v>
+        <v>-4.0674</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.956</v>
+        <v>-1.9335</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1973</v>
+        <v>-2.1338</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5785</v>
+        <v>-1.8763</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3543</v>
+        <v>-1.2974</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2241</v>
+        <v>-0.579</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8198</v>
+        <v>-2.191</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3983</v>
+        <v>-0.6362</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4215</v>
+        <v>-1.5549</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8214</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4908</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6694</v>
+        <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.0561</v>
+        <v>0.6073</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2284</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.8277</v>
+        <v>0.0262</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,16 +1189,16 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.909200000000002</v>
+        <v>-5.2505</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.219200000000001</v>
+        <v>-6.560500000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3101</v>
+        <v>1.31</v>
       </c>
       <c r="G10" t="n">
-        <v>1.341200000000001</v>
+        <v>1.3412</v>
       </c>
       <c r="H10" t="n">
         <v>7.380000000000001</v>
@@ -1210,13 +1210,13 @@
         <v>1.621999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8481</v>
+        <v>3.848100000000001</v>
       </c>
       <c r="L10" t="n">
         <v>-2.226</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2806999999999995</v>
+        <v>-0.2806999999999996</v>
       </c>
       <c r="N10" t="n">
         <v>3.5318</v>
@@ -1234,13 +1234,13 @@
         <v>13.3472</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0534</v>
+        <v>-1.3947</v>
       </c>
       <c r="T10" t="n">
-        <v>4.0276</v>
+        <v>4.6863</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.081</v>
+        <v>-6.0812</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1171</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2111</v>
+        <v>3.6671</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0659</v>
+        <v>2.1244</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1452</v>
+        <v>1.5427</v>
       </c>
       <c r="G11" t="n">
         <v>2.1867</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9895</v>
+        <v>0.4456</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6464</v>
+        <v>0.705</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6569</v>
+        <v>-0.2594</v>
       </c>
       <c r="V11" t="n">
         <v>0.8295</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.7149</v>
+        <v>3.5214</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9291</v>
+        <v>1.4061</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7858</v>
+        <v>2.1153</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0472</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1728</v>
+        <v>0.9792</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6856</v>
+        <v>0.1626</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4872</v>
+        <v>0.8167</v>
       </c>
       <c r="V12" t="n">
         <v>2.3573</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.7337</v>
+        <v>2.6622</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1217</v>
+        <v>1.7033</v>
       </c>
       <c r="F13" t="n">
-        <v>0.612</v>
+        <v>0.9589</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0469</v>
@@ -1468,13 +1468,13 @@
         <v>2.0534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7271</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3829</v>
+        <v>0.9645</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6558</v>
+        <v>-0.3088</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0238</v>
+        <v>2.4089</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1709</v>
+        <v>1.9724</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1472</v>
+        <v>0.4365</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4629</v>
+        <v>-0.0034</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5187</v>
+        <v>-0.1007</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9817</v>
+        <v>0.0973</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8539</v>
+        <v>0.5585</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6171</v>
+        <v>1.2298</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2368</v>
+        <v>-0.6713</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.391</v>
+        <v>-0.5619</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1358</v>
+        <v>-1.3305</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7449</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0267</v>
+        <v>2.2588</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0534</v>
+        <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7744</v>
+        <v>0.9831</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3438</v>
+        <v>1.4139</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5694</v>
+        <v>-0.4308</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2402</v>
+        <v>-0.8295</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9539</v>
+        <v>1.4537</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4494</v>
+        <v>1.3341</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.1196</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0034</v>
+        <v>0.4629</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1007</v>
+        <v>-0.5187</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0973</v>
+        <v>0.9817</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5585</v>
+        <v>0.8539</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2298</v>
+        <v>0.6171</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6713</v>
+        <v>0.2368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5619</v>
+        <v>-0.391</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3305</v>
+        <v>-1.1358</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7449</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2588</v>
+        <v>1.0267</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2588</v>
+        <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5281</v>
+        <v>0.2043</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8909</v>
+        <v>1.5069</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3628</v>
+        <v>-1.3026</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8295</v>
+        <v>-0.2402</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8295</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9657</v>
+        <v>1.4381</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0992</v>
+        <v>0.2038</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.2343</v>
       </c>
       <c r="G16" t="n">
         <v>0.3368</v>
@@ -1702,13 +1702,13 @@
         <v>1.0267</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6381</v>
+        <v>-0.1656</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5192</v>
+        <v>-0.4146</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1188</v>
+        <v>0.249</v>
       </c>
       <c r="V16" t="n">
         <v>0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7614</v>
+        <v>0.4694</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1695</v>
+        <v>-0.0189</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4081</v>
+        <v>0.4883</v>
       </c>
       <c r="G17" t="n">
         <v>2.4306</v>
@@ -1780,13 +1780,13 @@
         <v>2.0534</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6396</v>
+        <v>-0.4088</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7673</v>
+        <v>0.3833</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8723</v>
+        <v>-0.7921</v>
       </c>
       <c r="V17" t="n">
         <v>1.5277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.1562</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5532</v>
+        <v>-0.4486</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.283</v>
+        <v>0.2923</v>
       </c>
       <c r="G18" t="n">
         <v>1.0243</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4766</v>
+        <v>0.2034</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2558</v>
+        <v>-0.1512</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2208</v>
+        <v>0.3546</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1786</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3867</v>
+        <v>-1.0607</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.2332</v>
+        <v>-3.9193</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8465</v>
+        <v>2.8586</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6278</v>
@@ -1936,13 +1936,13 @@
         <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4731</v>
+        <v>0.7991</v>
       </c>
       <c r="T19" t="n">
-        <v>0.12</v>
+        <v>0.4338</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3532</v>
+        <v>0.3653</v>
       </c>
       <c r="V19" t="n">
         <v>1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.7094</v>
+        <v>-6.4026</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.1904</v>
+        <v>-5.6674</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.519</v>
+        <v>-0.7353</v>
       </c>
       <c r="G20" t="n">
         <v>-4.0574</v>
@@ -2014,13 +2014,13 @@
         <v>2.0534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1426</v>
+        <v>0.4494</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5538</v>
+        <v>1.0768</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4112</v>
+        <v>-0.6274</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7679</v>
@@ -2047,16 +2047,16 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>5.909400000000002</v>
+        <v>8.001299999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.310099999999998</v>
+        <v>-1.310099999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>7.2193</v>
+        <v>9.311199999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3414</v>
+        <v>-1.341400000000001</v>
       </c>
       <c r="H21" t="n">
         <v>-7.379799999999999</v>
@@ -2065,7 +2065,7 @@
         <v>6.0388</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2808000000000006</v>
+        <v>0.2807999999999997</v>
       </c>
       <c r="K21" t="n">
         <v>-3.5317</v>
@@ -2092,13 +2092,13 @@
         <v>16.4274</v>
       </c>
       <c r="S21" t="n">
-        <v>2.0533</v>
+        <v>4.1454</v>
       </c>
       <c r="T21" t="n">
-        <v>6.0811</v>
+        <v>6.081</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.0276</v>
+        <v>-1.9355</v>
       </c>
       <c r="V21" t="n">
         <v>2.1171</v>
